--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486750_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486750_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8729</v>
+        <v>6.0843</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2368</v>
+        <v>3.7958</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6362</v>
+        <v>2.2885</v>
       </c>
       <c r="G2" t="n">
         <v>3.0197</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>3.023</v>
+        <v>1.2344</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7646</v>
+        <v>0.3237</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2584</v>
+        <v>0.9107</v>
       </c>
       <c r="V2" t="n">
         <v>0.2856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.57</v>
+        <v>5.123</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6336</v>
+        <v>3.006</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9364</v>
+        <v>2.1169</v>
       </c>
       <c r="G3" t="n">
         <v>3.2231</v>
@@ -688,13 +688,13 @@
         <v>3.0892</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7713</v>
+        <v>1.3243</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6901</v>
+        <v>-0.3177</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4614</v>
+        <v>1.642</v>
       </c>
       <c r="V3" t="n">
         <v>1.3479</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6614</v>
+        <v>4.9482</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2574</v>
+        <v>1.1469</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4039</v>
+        <v>3.8012</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4199</v>
@@ -766,13 +766,13 @@
         <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6178</v>
+        <v>0.669</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9933</v>
+        <v>-0.1038</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3755</v>
+        <v>0.7728</v>
       </c>
       <c r="V4" t="n">
         <v>3.1545</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4641</v>
+        <v>3.1219</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.118</v>
+        <v>0.5647</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5821</v>
+        <v>2.5573</v>
       </c>
       <c r="G5" t="n">
         <v>0.1139</v>
@@ -844,13 +844,13 @@
         <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4301</v>
+        <v>0.2277</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9381</v>
+        <v>-0.2554</v>
       </c>
       <c r="U5" t="n">
-        <v>0.508</v>
+        <v>0.4831</v>
       </c>
       <c r="V5" t="n">
         <v>0.6565</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0614</v>
+        <v>2.0668</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8492</v>
+        <v>-2.1665</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9106</v>
+        <v>4.2334</v>
       </c>
       <c r="G6" t="n">
         <v>1.5811</v>
@@ -922,13 +922,13 @@
         <v>2.7031</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6123</v>
+        <v>0.3932</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8277</v>
+        <v>-0.1451</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2154</v>
+        <v>0.5383</v>
       </c>
       <c r="V6" t="n">
         <v>0.2856</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6619</v>
+        <v>0.8205</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2887</v>
+        <v>2.4473</v>
       </c>
       <c r="F7" t="n">
         <v>-1.6268</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2483</v>
+        <v>-0.0897</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6622</v>
+        <v>-0.5036</v>
       </c>
       <c r="U7" t="n">
         <v>0.4139</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0609</v>
+        <v>0.0136</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1104</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0495</v>
+        <v>0.124</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0002</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0607</v>
+        <v>0.0138</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>S. GUTIERREZ ROA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7345</v>
+        <v>-2.1452</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3506</v>
+        <v>-0.2345</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0851</v>
+        <v>-1.9107</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6502</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8823</v>
+        <v>-0.2347</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7679</v>
+        <v>-0.4069</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2769</v>
+        <v>0.0414</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.399</v>
+        <v>0.0414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3733</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4833</v>
+        <v>-0.2761</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8899</v>
+        <v>-0.4069</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3901</v>
+        <v>-0.4689</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7168</v>
+        <v>-0.2759</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6733</v>
+        <v>-0.193</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4911</v>
+        <v>-1.2277</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3505</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. GUTIERREZ ROA</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.25</v>
+        <v>-2.5315</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2897</v>
+        <v>-0.4216</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9603</v>
+        <v>-2.1099</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-2.6502</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2347</v>
+        <v>-0.8823</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4069</v>
+        <v>-1.7679</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0414</v>
+        <v>-0.2769</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0414</v>
+        <v>-0.399</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.1221</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-2.3733</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2761</v>
+        <v>-0.4833</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4069</v>
+        <v>-1.8899</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1931</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5738</v>
+        <v>0.593</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3311</v>
+        <v>-0.0554</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2427</v>
+        <v>0.6484</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2277</v>
+        <v>0.4911</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2277</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5138</v>
+        <v>-3.0228</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2341</v>
+        <v>-1.9169</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2797</v>
+        <v>-1.1059</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6696</v>
@@ -1312,13 +1312,13 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4358</v>
+        <v>0.0552</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8277</v>
+        <v>-0.5105</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3919</v>
+        <v>0.5657</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0222</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5259</v>
+        <v>-4.1686</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3123</v>
+        <v>-2.1537</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2136</v>
+        <v>-2.015</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4514</v>
@@ -1390,13 +1390,13 @@
         <v>0.7723</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5848</v>
+        <v>-0.2276</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8277</v>
+        <v>-0.6691</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2429</v>
+        <v>0.4416</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3658</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.206600000000002</v>
+        <v>10.3102</v>
       </c>
       <c r="E13" t="n">
-        <v>2.853399999999999</v>
+        <v>3.957100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>6.353200000000001</v>
+        <v>6.352999999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>1.412799999999999</v>
+        <v>1.4128</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2053</v>
+        <v>6.205300000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-4.7926</v>
@@ -1468,16 +1468,16 @@
         <v>15.4462</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6208</v>
+        <v>3.7244</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7269</v>
+        <v>-2.6232</v>
       </c>
       <c r="U13" t="n">
         <v>6.3477</v>
       </c>
       <c r="V13" t="n">
-        <v>6.138499999999999</v>
+        <v>6.1385</v>
       </c>
       <c r="W13" t="n">
         <v>10.4651</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3536</v>
+        <v>3.573</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3297</v>
+        <v>3.2263</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0239</v>
+        <v>0.3467</v>
       </c>
       <c r="G14" t="n">
         <v>1.864</v>
@@ -1546,13 +1546,13 @@
         <v>2.51</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7229</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7729</v>
+        <v>-0.8763</v>
       </c>
       <c r="U14" t="n">
-        <v>0.05</v>
+        <v>0.3728</v>
       </c>
       <c r="V14" t="n">
         <v>2.5986</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9623</v>
+        <v>3.3015</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6742</v>
+        <v>4.0879</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7118</v>
+        <v>-0.7863</v>
       </c>
       <c r="G15" t="n">
         <v>5.2219</v>
@@ -1624,13 +1624,13 @@
         <v>2.51</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7116</v>
+        <v>-0.3724</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1865</v>
+        <v>-0.7728</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4749</v>
+        <v>0.4004</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1271</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6996</v>
+        <v>1.6747</v>
       </c>
       <c r="E16" t="n">
         <v>1.3652</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3344</v>
+        <v>0.3096</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4522</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0993</v>
+        <v>-0.1241</v>
       </c>
       <c r="T16" t="n">
         <v>-0.4691</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3698</v>
+        <v>0.345</v>
       </c>
       <c r="V16" t="n">
         <v>1.5133</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0646</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2304</v>
+        <v>-1.0236</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1328</v>
+        <v>0.959</v>
       </c>
       <c r="G17" t="n">
         <v>1.0583</v>
@@ -1780,13 +1780,13 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0054</v>
+        <v>0.0276</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6898</v>
+        <v>-0.483</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6844</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5712</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>A. ALONSO LANTIGUA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7756</v>
+        <v>-0.7512</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6358</v>
+        <v>-1.3069</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1399</v>
+        <v>0.5557</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9355</v>
+        <v>-0.9355</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7863</v>
+        <v>-2.5586</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1492</v>
+        <v>1.6231</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1506</v>
+        <v>0.4932</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3043</v>
+        <v>-0.9718</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1536</v>
+        <v>1.4649</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2151</v>
+        <v>-1.4286</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5179</v>
+        <v>-1.5868</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3029</v>
+        <v>0.1582</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2759</v>
+        <v>-0.3379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8556</v>
+        <v>-0.8347</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5797</v>
+        <v>0.4968</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2422</v>
+        <v>-0.0571</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2422</v>
+        <v>-0.0571</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALONSO LANTIGUA</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.805</v>
+        <v>-0.7756</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4103</v>
+        <v>-0.6358</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6054</v>
+        <v>-0.1399</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9355</v>
+        <v>0.9355</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5586</v>
+        <v>0.7863</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6231</v>
+        <v>0.1492</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4932</v>
+        <v>2.1506</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9718</v>
+        <v>2.3043</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4649</v>
+        <v>-0.1536</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4286</v>
+        <v>-1.2151</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5868</v>
+        <v>-1.5179</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1582</v>
+        <v>0.3029</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3916</v>
+        <v>-0.2759</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9381</v>
+        <v>-0.8556</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5465</v>
+        <v>0.5797</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0571</v>
+        <v>-1.2422</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0571</v>
+        <v>-1.2422</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1394</v>
+        <v>-1.1146</v>
       </c>
       <c r="E20" t="n">
         <v>0.1408</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2802</v>
+        <v>-1.2553</v>
       </c>
       <c r="G20" t="n">
         <v>0.2275</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4248</v>
+        <v>-0.4</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9421</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6308</v>
+        <v>-3.6443</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.731</v>
+        <v>-1.8686</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8998</v>
+        <v>-1.7757</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4749</v>
@@ -2092,13 +2092,13 @@
         <v>2.7031</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2408</v>
+        <v>0.2273</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8268</v>
+        <v>-0.3109</v>
       </c>
       <c r="U21" t="n">
-        <v>0.414</v>
+        <v>0.5381</v>
       </c>
       <c r="V21" t="n">
         <v>-3.169</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2118</v>
+        <v>-3.9512</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4618</v>
+        <v>-4.1516</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2501</v>
+        <v>0.2004</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8903</v>
@@ -2170,13 +2170,13 @@
         <v>1.5446</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3641</v>
+        <v>-0.1035</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9933</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6292</v>
+        <v>0.5795</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5712</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.5621</v>
+        <v>-7.4546</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.3937</v>
+        <v>-6.1869</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1684</v>
+        <v>-1.2677</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9671</v>
@@ -2248,13 +2248,13 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8661</v>
+        <v>-0.7585</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1036</v>
+        <v>-0.8968</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2376</v>
+        <v>0.1383</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5704</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.206799999999999</v>
+        <v>-9.206899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.3531</v>
+        <v>-6.353199999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.853499999999999</v>
+        <v>-2.8535</v>
       </c>
       <c r="G24" t="n">
         <v>-1.412799999999999</v>
@@ -2329,10 +2329,10 @@
         <v>-2.6209</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.3476</v>
+        <v>-6.3477</v>
       </c>
       <c r="U24" t="n">
-        <v>3.7269</v>
+        <v>3.7268</v>
       </c>
       <c r="V24" t="n">
         <v>-6.138400000000001</v>
